--- a/docs/直播数据管理设计方案/巨量引擎自定义报表数据.xlsx
+++ b/docs/直播数据管理设计方案/巨量引擎自定义报表数据.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报表数据" sheetId="1" r:id="Ra5632c9356f14d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报表数据" sheetId="1" r:id="R6ef4ce618f084938"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,12 +52,27 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24466B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDE7F2"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -125,7 +140,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -234,6 +249,96 @@
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -242,9 +347,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReportData" displayName="ReportData" ref="A2:AI26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A2:AI26"/>
-  <x:tableColumns count="35">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReportData" displayName="ReportData" ref="A2:AL26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A2:AL26"/>
+  <x:tableColumns count="38">
     <x:tableColumn id="1" name="stat_time_hour"/>
     <x:tableColumn id="2" name="stat_time_day"/>
     <x:tableColumn id="3" name="stat_time_month"/>
@@ -280,6 +385,9 @@
     <x:tableColumn id="33" name="live_component_click_count"/>
     <x:tableColumn id="34" name="live_component_click_cost"/>
     <x:tableColumn id="35" name="live_component_click_rate"/>
+    <x:tableColumn id="36" name="deep_convert_cnt"/>
+    <x:tableColumn id="37" name="deep_convert_cost"/>
+    <x:tableColumn id="38" name="deep_convert_rate"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -515,327 +623,357 @@
     <x:col min="33" max="33" width="25" hidden="0" customWidth="1"/>
     <x:col min="34" max="34" width="25" hidden="0" customWidth="1"/>
     <x:col min="35" max="35" width="25" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="25" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="25" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="45" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="45" t="str">
         <x:v>时间-小时</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="46" t="str">
         <x:v>时间-天</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="46" t="str">
         <x:v>时间-月</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="46" t="str">
         <x:v>消耗(元)</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="E1" s="46" t="str">
         <x:v>展示数</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="46" t="str">
         <x:v>平均千次展现费用(元)</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="G1" s="46" t="str">
         <x:v>点击数</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="46" t="str">
         <x:v>点击率</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="I1" s="46" t="str">
         <x:v>平均点击单价(元)</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="J1" s="46" t="str">
         <x:v>转化数(计费时间)</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="K1" s="46" t="str">
         <x:v>转化成本(计费时间)</x:v>
       </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="L1" s="46" t="str">
         <x:v>转化率(计费时间)</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="M1" s="46" t="str">
         <x:v>转化数</x:v>
       </x:c>
-      <x:c r="N1" s="9" t="str">
+      <x:c r="N1" s="46" t="str">
         <x:v>平均转化成本(元)</x:v>
       </x:c>
-      <x:c r="O1" s="9" t="str">
+      <x:c r="O1" s="46" t="str">
         <x:v>转化率</x:v>
       </x:c>
-      <x:c r="P1" s="9" t="str">
+      <x:c r="P1" s="46" t="str">
         <x:v>表单提交</x:v>
       </x:c>
-      <x:c r="Q1" s="9" t="str">
+      <x:c r="Q1" s="46" t="str">
         <x:v>附加创意表单提交</x:v>
       </x:c>
-      <x:c r="R1" s="9" t="str">
+      <x:c r="R1" s="46" t="str">
         <x:v>有效咨询</x:v>
       </x:c>
-      <x:c r="S1" s="9" t="str">
+      <x:c r="S1" s="46" t="str">
         <x:v>表单提交(计费时间)</x:v>
       </x:c>
-      <x:c r="T1" s="9" t="str">
+      <x:c r="T1" s="46" t="str">
         <x:v>表单提交数(包含附加创意表单数)</x:v>
       </x:c>
-      <x:c r="U1" s="9" t="str">
+      <x:c r="U1" s="46" t="str">
         <x:v>表单提交成本(包含附加创意表单数)</x:v>
       </x:c>
-      <x:c r="V1" s="9" t="str">
+      <x:c r="V1" s="46" t="str">
         <x:v>保险支付数</x:v>
       </x:c>
-      <x:c r="W1" s="9" t="str">
+      <x:c r="W1" s="46" t="str">
         <x:v>保险支付成本(元)</x:v>
       </x:c>
-      <x:c r="X1" s="9" t="str">
+      <x:c r="X1" s="46" t="str">
         <x:v>保费成交金额</x:v>
       </x:c>
-      <x:c r="Y1" s="9" t="str">
+      <x:c r="Y1" s="46" t="str">
         <x:v>保费成交ROI</x:v>
       </x:c>
-      <x:c r="Z1" s="9" t="str">
+      <x:c r="Z1" s="46" t="str">
         <x:v>保费成交金额（计费时间）</x:v>
       </x:c>
-      <x:c r="AA1" s="9" t="str">
+      <x:c r="AA1" s="46" t="str">
         <x:v>保费成交ROI（计费时间）</x:v>
       </x:c>
-      <x:c r="AB1" s="9" t="str">
+      <x:c r="AB1" s="46" t="str">
         <x:v>直播间观看数</x:v>
       </x:c>
-      <x:c r="AC1" s="9" t="str">
+      <x:c r="AC1" s="46" t="str">
         <x:v>直播间超过1分钟观看数</x:v>
       </x:c>
-      <x:c r="AD1" s="9" t="str">
+      <x:c r="AD1" s="46" t="str">
         <x:v>直播间关注数</x:v>
       </x:c>
-      <x:c r="AE1" s="9" t="str">
+      <x:c r="AE1" s="46" t="str">
         <x:v>直播间分享数</x:v>
       </x:c>
-      <x:c r="AF1" s="9" t="str">
+      <x:c r="AF1" s="46" t="str">
         <x:v>直播间评论数</x:v>
       </x:c>
-      <x:c r="AG1" s="9" t="str">
+      <x:c r="AG1" s="46" t="str">
         <x:v>组件点击数</x:v>
       </x:c>
-      <x:c r="AH1" s="9" t="str">
+      <x:c r="AH1" s="46" t="str">
         <x:v>组件点击成本</x:v>
       </x:c>
-      <x:c r="AI1" s="10" t="str">
+      <x:c r="AI1" s="46" t="str">
         <x:v>组件点击率</x:v>
+      </x:c>
+      <x:c r="AJ1" s="46" t="str">
+        <x:v>深度转化数</x:v>
+      </x:c>
+      <x:c r="AK1" s="46" t="str">
+        <x:v>深度转化成本(元)</x:v>
+      </x:c>
+      <x:c r="AL1" s="47" t="str">
+        <x:v>深度转化率</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="60" customHeight="1">
-      <x:c r="A2" s="8" t="str">
+      <x:c r="A2" s="45" t="str">
         <x:v>stat_time_hour</x:v>
       </x:c>
-      <x:c r="B2" s="9" t="str">
+      <x:c r="B2" s="46" t="str">
         <x:v>stat_time_day</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="str">
+      <x:c r="C2" s="46" t="str">
         <x:v>stat_time_month</x:v>
       </x:c>
-      <x:c r="D2" s="9" t="str">
+      <x:c r="D2" s="46" t="str">
         <x:v>stat_cost</x:v>
       </x:c>
-      <x:c r="E2" s="9" t="str">
+      <x:c r="E2" s="46" t="str">
         <x:v>show_cnt</x:v>
       </x:c>
-      <x:c r="F2" s="9" t="str">
+      <x:c r="F2" s="46" t="str">
         <x:v>cpm_platform</x:v>
       </x:c>
-      <x:c r="G2" s="9" t="str">
+      <x:c r="G2" s="46" t="str">
         <x:v>click_cnt</x:v>
       </x:c>
-      <x:c r="H2" s="9" t="str">
+      <x:c r="H2" s="46" t="str">
         <x:v>ctr</x:v>
       </x:c>
-      <x:c r="I2" s="9" t="str">
+      <x:c r="I2" s="46" t="str">
         <x:v>cpc_platform</x:v>
       </x:c>
-      <x:c r="J2" s="9" t="str">
+      <x:c r="J2" s="46" t="str">
         <x:v>attribution_convert_cnt</x:v>
       </x:c>
-      <x:c r="K2" s="9" t="str">
+      <x:c r="K2" s="46" t="str">
         <x:v>attribution_convert_cost</x:v>
       </x:c>
-      <x:c r="L2" s="9" t="str">
+      <x:c r="L2" s="46" t="str">
         <x:v>attribution_conversion_rate</x:v>
       </x:c>
-      <x:c r="M2" s="9" t="str">
+      <x:c r="M2" s="46" t="str">
         <x:v>convert_cnt</x:v>
       </x:c>
-      <x:c r="N2" s="9" t="str">
+      <x:c r="N2" s="46" t="str">
         <x:v>conversion_cost</x:v>
       </x:c>
-      <x:c r="O2" s="9" t="str">
+      <x:c r="O2" s="46" t="str">
         <x:v>conversion_rate</x:v>
       </x:c>
-      <x:c r="P2" s="9" t="str">
+      <x:c r="P2" s="46" t="str">
         <x:v>form</x:v>
       </x:c>
-      <x:c r="Q2" s="9" t="str">
+      <x:c r="Q2" s="46" t="str">
         <x:v>form_submit</x:v>
       </x:c>
-      <x:c r="R2" s="9" t="str">
+      <x:c r="R2" s="46" t="str">
         <x:v>consult_effective</x:v>
       </x:c>
-      <x:c r="S2" s="9" t="str">
+      <x:c r="S2" s="46" t="str">
         <x:v>attribution_form</x:v>
       </x:c>
-      <x:c r="T2" s="9" t="str">
+      <x:c r="T2" s="46" t="str">
         <x:v>form_and_submit_count</x:v>
       </x:c>
-      <x:c r="U2" s="9" t="str">
+      <x:c r="U2" s="46" t="str">
         <x:v>form_and_submit_cost</x:v>
       </x:c>
-      <x:c r="V2" s="9" t="str">
+      <x:c r="V2" s="46" t="str">
         <x:v>premium_payment_count</x:v>
       </x:c>
-      <x:c r="W2" s="9" t="str">
+      <x:c r="W2" s="46" t="str">
         <x:v>premium_payment_cost</x:v>
       </x:c>
-      <x:c r="X2" s="9" t="str">
+      <x:c r="X2" s="46" t="str">
         <x:v>stat_insurance_payment_pay_amount</x:v>
       </x:c>
-      <x:c r="Y2" s="9" t="str">
+      <x:c r="Y2" s="46" t="str">
         <x:v>stat_insurance_payment_roi</x:v>
       </x:c>
-      <x:c r="Z2" s="9" t="str">
+      <x:c r="Z2" s="46" t="str">
         <x:v>attribution_insurance_payment_pay_amount</x:v>
       </x:c>
-      <x:c r="AA2" s="9" t="str">
+      <x:c r="AA2" s="46" t="str">
         <x:v>attribution_insurance_payment_roi</x:v>
       </x:c>
-      <x:c r="AB2" s="9" t="str">
+      <x:c r="AB2" s="46" t="str">
         <x:v>luban_live_enter_cnt</x:v>
       </x:c>
-      <x:c r="AC2" s="9" t="str">
+      <x:c r="AC2" s="46" t="str">
         <x:v>live_watch_one_minute_count</x:v>
       </x:c>
-      <x:c r="AD2" s="9" t="str">
+      <x:c r="AD2" s="46" t="str">
         <x:v>luban_live_follow_cnt</x:v>
       </x:c>
-      <x:c r="AE2" s="9" t="str">
+      <x:c r="AE2" s="46" t="str">
         <x:v>luban_live_share_cnt</x:v>
       </x:c>
-      <x:c r="AF2" s="9" t="str">
+      <x:c r="AF2" s="46" t="str">
         <x:v>luban_live_comment_cnt</x:v>
       </x:c>
-      <x:c r="AG2" s="9" t="str">
+      <x:c r="AG2" s="46" t="str">
         <x:v>live_component_click_count</x:v>
       </x:c>
-      <x:c r="AH2" s="9" t="str">
+      <x:c r="AH2" s="46" t="str">
         <x:v>live_component_click_cost</x:v>
       </x:c>
-      <x:c r="AI2" s="10" t="str">
+      <x:c r="AI2" s="46" t="str">
         <x:v>live_component_click_rate</x:v>
+      </x:c>
+      <x:c r="AJ2" s="46" t="str">
+        <x:v>deep_convert_cnt</x:v>
+      </x:c>
+      <x:c r="AK2" s="46" t="str">
+        <x:v>deep_convert_cost</x:v>
+      </x:c>
+      <x:c r="AL2" s="47" t="str">
+        <x:v>deep_convert_rate</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
-      <x:c r="A3" s="17" t="str">
+      <x:c r="A3" s="52" t="str">
         <x:v>2026-10-18 07:00 - 07:59</x:v>
       </x:c>
-      <x:c r="B3" s="18" t="d">
+      <x:c r="B3" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="str">
+      <x:c r="C3" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="n">
+      <x:c r="D3" s="54" t="n">
         <x:v>3190.82</x:v>
       </x:c>
-      <x:c r="E3" s="20" t="n">
+      <x:c r="E3" s="55" t="n">
         <x:v>21101</x:v>
       </x:c>
-      <x:c r="F3" s="19" t="n">
+      <x:c r="F3" s="54" t="n">
         <x:v>151.22</x:v>
       </x:c>
-      <x:c r="G3" s="20" t="n">
+      <x:c r="G3" s="55" t="n">
         <x:v>466</x:v>
       </x:c>
-      <x:c r="H3" s="21" t="n">
+      <x:c r="H3" s="56" t="n">
         <x:v>0.022099999999999998</x:v>
       </x:c>
-      <x:c r="I3" s="19" t="n">
+      <x:c r="I3" s="54" t="n">
         <x:v>6.85</x:v>
       </x:c>
-      <x:c r="J3" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L3" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M3" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O3" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P3" s="20" t="n">
+      <x:c r="J3" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L3" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O3" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P3" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q3" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R3" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S3" s="20" t="n">
+      <x:c r="Q3" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R3" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S3" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="T3" s="20" t="n">
+      <x:c r="T3" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="U3" s="19" t="n">
+      <x:c r="U3" s="54" t="n">
         <x:v>1595.41</x:v>
       </x:c>
-      <x:c r="V3" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA3" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB3" s="20" t="n">
+      <x:c r="V3" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB3" s="55" t="n">
         <x:v>542</x:v>
       </x:c>
-      <x:c r="AC3" s="20" t="n">
+      <x:c r="AC3" s="55" t="n">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="AD3" s="20" t="n">
+      <x:c r="AD3" s="55" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="AE3" s="20" t="n">
+      <x:c r="AE3" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AF3" s="20" t="n">
+      <x:c r="AF3" s="55" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="AG3" s="20" t="n">
+      <x:c r="AG3" s="55" t="n">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="AH3" s="19" t="n">
+      <x:c r="AH3" s="54" t="n">
         <x:v>29.27</x:v>
       </x:c>
-      <x:c r="AI3" s="21" t="n">
+      <x:c r="AI3" s="56" t="n">
         <x:v>0.16690000000000002</x:v>
+      </x:c>
+      <x:c r="AJ3" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK3" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL3" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
@@ -944,112 +1082,130 @@
       <x:c r="AI4" s="16" t="n">
         <x:v>0.102</x:v>
       </x:c>
+      <x:c r="AJ4" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL4" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
-      <x:c r="A5" s="17" t="str">
+      <x:c r="A5" s="52" t="str">
         <x:v>2026-10-18 13:00 - 13:59</x:v>
       </x:c>
-      <x:c r="B5" s="18" t="d">
+      <x:c r="B5" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
+      <x:c r="C5" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D5" s="19" t="n">
+      <x:c r="D5" s="54" t="n">
         <x:v>1975.22</x:v>
       </x:c>
-      <x:c r="E5" s="20" t="n">
+      <x:c r="E5" s="55" t="n">
         <x:v>10296</x:v>
       </x:c>
-      <x:c r="F5" s="19" t="n">
+      <x:c r="F5" s="54" t="n">
         <x:v>191.84</x:v>
       </x:c>
-      <x:c r="G5" s="20" t="n">
+      <x:c r="G5" s="55" t="n">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="H5" s="21" t="n">
+      <x:c r="H5" s="56" t="n">
         <x:v>0.0333</x:v>
       </x:c>
-      <x:c r="I5" s="19" t="n">
+      <x:c r="I5" s="54" t="n">
         <x:v>5.76</x:v>
       </x:c>
-      <x:c r="J5" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K5" s="19" t="n">
+      <x:c r="J5" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K5" s="54" t="n">
         <x:v>1975.22</x:v>
       </x:c>
-      <x:c r="L5" s="21" t="n">
+      <x:c r="L5" s="56" t="n">
         <x:v>0.0029</x:v>
       </x:c>
-      <x:c r="M5" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N5" s="19" t="n">
+      <x:c r="M5" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N5" s="54" t="n">
         <x:v>1975.22</x:v>
       </x:c>
-      <x:c r="O5" s="21" t="n">
+      <x:c r="O5" s="56" t="n">
         <x:v>0.0029</x:v>
       </x:c>
-      <x:c r="P5" s="20" t="n">
+      <x:c r="P5" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q5" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R5" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S5" s="20" t="n">
+      <x:c r="Q5" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="T5" s="20" t="n">
+      <x:c r="T5" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="U5" s="19" t="n">
+      <x:c r="U5" s="54" t="n">
         <x:v>658.41</x:v>
       </x:c>
-      <x:c r="V5" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W5" s="19" t="n">
+      <x:c r="V5" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W5" s="54" t="n">
         <x:v>1975.22</x:v>
       </x:c>
-      <x:c r="X5" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y5" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z5" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA5" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB5" s="20" t="n">
+      <x:c r="X5" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y5" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z5" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA5" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB5" s="55" t="n">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="AC5" s="20" t="n">
+      <x:c r="AC5" s="55" t="n">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="AD5" s="20" t="n">
+      <x:c r="AD5" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE5" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF5" s="20" t="n">
+      <x:c r="AE5" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF5" s="55" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="AG5" s="20" t="n">
+      <x:c r="AG5" s="55" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="AH5" s="19" t="n">
+      <x:c r="AH5" s="54" t="n">
         <x:v>50.65</x:v>
       </x:c>
-      <x:c r="AI5" s="21" t="n">
+      <x:c r="AI5" s="56" t="n">
         <x:v>0.0736</x:v>
+      </x:c>
+      <x:c r="AJ5" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK5" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL5" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
@@ -1158,112 +1314,130 @@
       <x:c r="AI6" s="16" t="n">
         <x:v>0.0705</x:v>
       </x:c>
+      <x:c r="AJ6" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL6" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
-      <x:c r="A7" s="17" t="str">
+      <x:c r="A7" s="52" t="str">
         <x:v>2026-10-18 09:00 - 09:59</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="d">
+      <x:c r="B7" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="str">
+      <x:c r="C7" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D7" s="19" t="n">
+      <x:c r="D7" s="54" t="n">
         <x:v>1580.52</x:v>
       </x:c>
-      <x:c r="E7" s="20" t="n">
+      <x:c r="E7" s="55" t="n">
         <x:v>10399</x:v>
       </x:c>
-      <x:c r="F7" s="19" t="n">
+      <x:c r="F7" s="54" t="n">
         <x:v>151.99</x:v>
       </x:c>
-      <x:c r="G7" s="20" t="n">
+      <x:c r="G7" s="55" t="n">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="H7" s="21" t="n">
+      <x:c r="H7" s="56" t="n">
         <x:v>0.0274</x:v>
       </x:c>
-      <x:c r="I7" s="19" t="n">
+      <x:c r="I7" s="54" t="n">
         <x:v>5.55</x:v>
       </x:c>
-      <x:c r="J7" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q7" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R7" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S7" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T7" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U7" s="19" t="n">
+      <x:c r="J7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T7" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U7" s="54" t="n">
         <x:v>1580.52</x:v>
       </x:c>
-      <x:c r="V7" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA7" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB7" s="20" t="n">
+      <x:c r="V7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB7" s="55" t="n">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="AC7" s="20" t="n">
+      <x:c r="AC7" s="55" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="AD7" s="20" t="n">
+      <x:c r="AD7" s="55" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="AE7" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF7" s="20" t="n">
+      <x:c r="AE7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF7" s="55" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="AG7" s="20" t="n">
+      <x:c r="AG7" s="55" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="AH7" s="19" t="n">
+      <x:c r="AH7" s="54" t="n">
         <x:v>32.93</x:v>
       </x:c>
-      <x:c r="AI7" s="21" t="n">
+      <x:c r="AI7" s="56" t="n">
         <x:v>0.10859999999999999</x:v>
+      </x:c>
+      <x:c r="AJ7" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK7" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL7" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
@@ -1372,112 +1546,130 @@
       <x:c r="AI8" s="16" t="n">
         <x:v>0.0833</x:v>
       </x:c>
+      <x:c r="AJ8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL8" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
-      <x:c r="A9" s="17" t="str">
+      <x:c r="A9" s="52" t="str">
         <x:v>2026-10-18 15:00 - 15:59</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="d">
+      <x:c r="B9" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str">
+      <x:c r="C9" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D9" s="19" t="n">
+      <x:c r="D9" s="54" t="n">
         <x:v>1556.64</x:v>
       </x:c>
-      <x:c r="E9" s="20" t="n">
+      <x:c r="E9" s="55" t="n">
         <x:v>7529</x:v>
       </x:c>
-      <x:c r="F9" s="19" t="n">
+      <x:c r="F9" s="54" t="n">
         <x:v>206.75</x:v>
       </x:c>
-      <x:c r="G9" s="20" t="n">
+      <x:c r="G9" s="55" t="n">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="H9" s="21" t="n">
+      <x:c r="H9" s="56" t="n">
         <x:v>0.0383</x:v>
       </x:c>
-      <x:c r="I9" s="19" t="n">
+      <x:c r="I9" s="54" t="n">
         <x:v>5.41</x:v>
       </x:c>
-      <x:c r="J9" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
+      <x:c r="J9" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="54" t="n">
         <x:v>1556.64</x:v>
       </x:c>
-      <x:c r="L9" s="21" t="n">
+      <x:c r="L9" s="56" t="n">
         <x:v>0.0034999999999999996</x:v>
       </x:c>
-      <x:c r="M9" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N9" s="19" t="n">
+      <x:c r="M9" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N9" s="54" t="n">
         <x:v>1556.64</x:v>
       </x:c>
-      <x:c r="O9" s="21" t="n">
+      <x:c r="O9" s="56" t="n">
         <x:v>0.0034999999999999996</x:v>
       </x:c>
-      <x:c r="P9" s="20" t="n">
+      <x:c r="P9" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q9" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R9" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S9" s="20" t="n">
+      <x:c r="Q9" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="T9" s="20" t="n">
+      <x:c r="T9" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="U9" s="19" t="n">
+      <x:c r="U9" s="54" t="n">
         <x:v>778.32</x:v>
       </x:c>
-      <x:c r="V9" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W9" s="19" t="n">
+      <x:c r="V9" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W9" s="54" t="n">
         <x:v>1556.64</x:v>
       </x:c>
-      <x:c r="X9" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y9" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z9" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA9" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB9" s="20" t="n">
+      <x:c r="X9" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y9" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z9" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA9" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB9" s="55" t="n">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="AC9" s="20" t="n">
+      <x:c r="AC9" s="55" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="AD9" s="20" t="n">
+      <x:c r="AD9" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE9" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF9" s="20" t="n">
+      <x:c r="AE9" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF9" s="55" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="AG9" s="20" t="n">
+      <x:c r="AG9" s="55" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="AH9" s="19" t="n">
+      <x:c r="AH9" s="54" t="n">
         <x:v>37.97</x:v>
       </x:c>
-      <x:c r="AI9" s="21" t="n">
+      <x:c r="AI9" s="56" t="n">
         <x:v>0.1033</x:v>
+      </x:c>
+      <x:c r="AJ9" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK9" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL9" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
@@ -1586,112 +1778,130 @@
       <x:c r="AI10" s="16" t="n">
         <x:v>0.1213</x:v>
       </x:c>
+      <x:c r="AJ10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK10" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL10" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
-      <x:c r="A11" s="17" t="str">
+      <x:c r="A11" s="52" t="str">
         <x:v>2026-10-18 06:00 - 06:59</x:v>
       </x:c>
-      <x:c r="B11" s="18" t="d">
+      <x:c r="B11" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str">
+      <x:c r="C11" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D11" s="19" t="n">
+      <x:c r="D11" s="54" t="n">
         <x:v>1491.14</x:v>
       </x:c>
-      <x:c r="E11" s="20" t="n">
+      <x:c r="E11" s="55" t="n">
         <x:v>11831</x:v>
       </x:c>
-      <x:c r="F11" s="19" t="n">
+      <x:c r="F11" s="54" t="n">
         <x:v>126.04</x:v>
       </x:c>
-      <x:c r="G11" s="20" t="n">
+      <x:c r="G11" s="55" t="n">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="H11" s="21" t="n">
+      <x:c r="H11" s="56" t="n">
         <x:v>0.0255</x:v>
       </x:c>
-      <x:c r="I11" s="19" t="n">
+      <x:c r="I11" s="54" t="n">
         <x:v>4.94</x:v>
       </x:c>
-      <x:c r="J11" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="J11" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="54" t="n">
         <x:v>1491.14</x:v>
       </x:c>
-      <x:c r="L11" s="21" t="n">
+      <x:c r="L11" s="56" t="n">
         <x:v>0.0033</x:v>
       </x:c>
-      <x:c r="M11" s="20" t="n">
+      <x:c r="M11" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N11" s="19" t="n">
+      <x:c r="N11" s="54" t="n">
         <x:v>745.57</x:v>
       </x:c>
-      <x:c r="O11" s="21" t="n">
+      <x:c r="O11" s="56" t="n">
         <x:v>0.0066</x:v>
       </x:c>
-      <x:c r="P11" s="20" t="n">
+      <x:c r="P11" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q11" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R11" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S11" s="20" t="n">
+      <x:c r="Q11" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="T11" s="20" t="n">
+      <x:c r="T11" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="U11" s="19" t="n">
+      <x:c r="U11" s="54" t="n">
         <x:v>497.05</x:v>
       </x:c>
-      <x:c r="V11" s="20" t="n">
+      <x:c r="V11" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="W11" s="19" t="n">
+      <x:c r="W11" s="54" t="n">
         <x:v>745.57</x:v>
       </x:c>
-      <x:c r="X11" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y11" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z11" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA11" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB11" s="20" t="n">
+      <x:c r="X11" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y11" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z11" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA11" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB11" s="55" t="n">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="AC11" s="20" t="n">
+      <x:c r="AC11" s="55" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="AD11" s="20" t="n">
+      <x:c r="AD11" s="55" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="AE11" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF11" s="20" t="n">
+      <x:c r="AE11" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF11" s="55" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AG11" s="20" t="n">
+      <x:c r="AG11" s="55" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="AH11" s="19" t="n">
+      <x:c r="AH11" s="54" t="n">
         <x:v>28.13</x:v>
       </x:c>
-      <x:c r="AI11" s="21" t="n">
+      <x:c r="AI11" s="56" t="n">
         <x:v>0.128</x:v>
+      </x:c>
+      <x:c r="AJ11" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK11" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL11" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
@@ -1800,112 +2010,130 @@
       <x:c r="AI12" s="16" t="n">
         <x:v>0.056600000000000004</x:v>
       </x:c>
+      <x:c r="AJ12" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL12" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
-      <x:c r="A13" s="17" t="str">
+      <x:c r="A13" s="52" t="str">
         <x:v>2026-10-18 17:00 - 17:59</x:v>
       </x:c>
-      <x:c r="B13" s="18" t="d">
+      <x:c r="B13" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str">
+      <x:c r="C13" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="n">
+      <x:c r="D13" s="54" t="n">
         <x:v>1183.5</x:v>
       </x:c>
-      <x:c r="E13" s="20" t="n">
+      <x:c r="E13" s="55" t="n">
         <x:v>8567</x:v>
       </x:c>
-      <x:c r="F13" s="19" t="n">
+      <x:c r="F13" s="54" t="n">
         <x:v>138.15</x:v>
       </x:c>
-      <x:c r="G13" s="20" t="n">
+      <x:c r="G13" s="55" t="n">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="H13" s="21" t="n">
+      <x:c r="H13" s="56" t="n">
         <x:v>0.0305</x:v>
       </x:c>
-      <x:c r="I13" s="19" t="n">
+      <x:c r="I13" s="54" t="n">
         <x:v>4.53</x:v>
       </x:c>
-      <x:c r="J13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N13" s="19" t="n">
+      <x:c r="J13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N13" s="54" t="n">
         <x:v>1183.5</x:v>
       </x:c>
-      <x:c r="O13" s="21" t="n">
+      <x:c r="O13" s="56" t="n">
         <x:v>0.0038</x:v>
       </x:c>
-      <x:c r="P13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U13" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V13" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W13" s="19" t="n">
+      <x:c r="P13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W13" s="54" t="n">
         <x:v>1183.5</x:v>
       </x:c>
-      <x:c r="X13" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y13" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z13" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA13" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB13" s="20" t="n">
+      <x:c r="X13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB13" s="55" t="n">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="AC13" s="20" t="n">
+      <x:c r="AC13" s="55" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="AD13" s="20" t="n">
+      <x:c r="AD13" s="55" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="AE13" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF13" s="20" t="n">
+      <x:c r="AE13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF13" s="55" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="AG13" s="20" t="n">
+      <x:c r="AG13" s="55" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="AH13" s="19" t="n">
+      <x:c r="AH13" s="54" t="n">
         <x:v>38.18</x:v>
       </x:c>
-      <x:c r="AI13" s="21" t="n">
+      <x:c r="AI13" s="56" t="n">
         <x:v>0.0721</x:v>
+      </x:c>
+      <x:c r="AJ13" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK13" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL13" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
@@ -2014,112 +2242,130 @@
       <x:c r="AI14" s="16" t="n">
         <x:v>0.1042</x:v>
       </x:c>
+      <x:c r="AJ14" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK14" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL14" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
-      <x:c r="A15" s="17" t="str">
+      <x:c r="A15" s="52" t="str">
         <x:v>2026-10-18 03:00 - 03:59</x:v>
       </x:c>
-      <x:c r="B15" s="18" t="d">
+      <x:c r="B15" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str">
+      <x:c r="C15" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D15" s="19" t="n">
+      <x:c r="D15" s="54" t="n">
         <x:v>1107.67</x:v>
       </x:c>
-      <x:c r="E15" s="20" t="n">
+      <x:c r="E15" s="55" t="n">
         <x:v>9616</x:v>
       </x:c>
-      <x:c r="F15" s="19" t="n">
+      <x:c r="F15" s="54" t="n">
         <x:v>115.19</x:v>
       </x:c>
-      <x:c r="G15" s="20" t="n">
+      <x:c r="G15" s="55" t="n">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="H15" s="21" t="n">
+      <x:c r="H15" s="56" t="n">
         <x:v>0.0369</x:v>
       </x:c>
-      <x:c r="I15" s="19" t="n">
+      <x:c r="I15" s="54" t="n">
         <x:v>3.12</x:v>
       </x:c>
-      <x:c r="J15" s="20" t="n">
+      <x:c r="J15" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K15" s="54" t="n">
         <x:v>553.84</x:v>
       </x:c>
-      <x:c r="L15" s="21" t="n">
+      <x:c r="L15" s="56" t="n">
         <x:v>0.005600000000000001</x:v>
       </x:c>
-      <x:c r="M15" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P15" s="20" t="n">
+      <x:c r="M15" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="55" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="Q15" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R15" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S15" s="20" t="n">
+      <x:c r="Q15" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R15" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" s="55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="T15" s="20" t="n">
+      <x:c r="T15" s="55" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="U15" s="19" t="n">
+      <x:c r="U15" s="54" t="n">
         <x:v>276.92</x:v>
       </x:c>
-      <x:c r="V15" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W15" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X15" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y15" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z15" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA15" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB15" s="20" t="n">
+      <x:c r="V15" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB15" s="55" t="n">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="AC15" s="20" t="n">
+      <x:c r="AC15" s="55" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="AD15" s="20" t="n">
+      <x:c r="AD15" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE15" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF15" s="20" t="n">
+      <x:c r="AE15" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF15" s="55" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="AG15" s="20" t="n">
+      <x:c r="AG15" s="55" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AH15" s="19" t="n">
+      <x:c r="AH15" s="54" t="n">
         <x:v>32.58</x:v>
       </x:c>
-      <x:c r="AI15" s="21" t="n">
+      <x:c r="AI15" s="56" t="n">
         <x:v>0.057</x:v>
+      </x:c>
+      <x:c r="AJ15" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK15" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL15" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -2228,112 +2474,130 @@
       <x:c r="AI16" s="16" t="n">
         <x:v>0.0507</x:v>
       </x:c>
+      <x:c r="AJ16" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK16" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL16" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
-      <x:c r="A17" s="17" t="str">
+      <x:c r="A17" s="52" t="str">
         <x:v>2026-10-18 21:00 - 21:59</x:v>
       </x:c>
-      <x:c r="B17" s="18" t="d">
+      <x:c r="B17" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str">
+      <x:c r="C17" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D17" s="19" t="n">
+      <x:c r="D17" s="54" t="n">
         <x:v>1016.7</x:v>
       </x:c>
-      <x:c r="E17" s="20" t="n">
+      <x:c r="E17" s="55" t="n">
         <x:v>7384</x:v>
       </x:c>
-      <x:c r="F17" s="19" t="n">
+      <x:c r="F17" s="54" t="n">
         <x:v>137.69</x:v>
       </x:c>
-      <x:c r="G17" s="20" t="n">
+      <x:c r="G17" s="55" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H17" s="21" t="n">
+      <x:c r="H17" s="56" t="n">
         <x:v>0.028399999999999998</x:v>
       </x:c>
-      <x:c r="I17" s="19" t="n">
+      <x:c r="I17" s="54" t="n">
         <x:v>4.84</x:v>
       </x:c>
-      <x:c r="J17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O17" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V17" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB17" s="20" t="n">
+      <x:c r="J17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB17" s="55" t="n">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="AC17" s="20" t="n">
+      <x:c r="AC17" s="55" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="AD17" s="20" t="n">
+      <x:c r="AD17" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AE17" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF17" s="20" t="n">
+      <x:c r="AE17" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF17" s="55" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="AG17" s="20" t="n">
+      <x:c r="AG17" s="55" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="AH17" s="19" t="n">
+      <x:c r="AH17" s="54" t="n">
         <x:v>40.67</x:v>
       </x:c>
-      <x:c r="AI17" s="21" t="n">
+      <x:c r="AI17" s="56" t="n">
         <x:v>0.085</x:v>
+      </x:c>
+      <x:c r="AJ17" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK17" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL17" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
@@ -2442,112 +2706,130 @@
       <x:c r="AI18" s="16" t="n">
         <x:v>0.1303</x:v>
       </x:c>
+      <x:c r="AJ18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL18" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="17" t="str">
+      <x:c r="A19" s="52" t="str">
         <x:v>2026-10-18 01:00 - 01:59</x:v>
       </x:c>
-      <x:c r="B19" s="18" t="d">
+      <x:c r="B19" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="str">
+      <x:c r="C19" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D19" s="19" t="n">
+      <x:c r="D19" s="54" t="n">
         <x:v>963.65</x:v>
       </x:c>
-      <x:c r="E19" s="20" t="n">
+      <x:c r="E19" s="55" t="n">
         <x:v>8102</x:v>
       </x:c>
-      <x:c r="F19" s="19" t="n">
+      <x:c r="F19" s="54" t="n">
         <x:v>118.94</x:v>
       </x:c>
-      <x:c r="G19" s="20" t="n">
+      <x:c r="G19" s="55" t="n">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H19" s="21" t="n">
+      <x:c r="H19" s="56" t="n">
         <x:v>0.0281</x:v>
       </x:c>
-      <x:c r="I19" s="19" t="n">
+      <x:c r="I19" s="54" t="n">
         <x:v>4.23</x:v>
       </x:c>
-      <x:c r="J19" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="J19" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K19" s="54" t="n">
         <x:v>963.65</x:v>
       </x:c>
-      <x:c r="L19" s="21" t="n">
+      <x:c r="L19" s="56" t="n">
         <x:v>0.0044</x:v>
       </x:c>
-      <x:c r="M19" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N19" s="19" t="n">
+      <x:c r="M19" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N19" s="54" t="n">
         <x:v>963.65</x:v>
       </x:c>
-      <x:c r="O19" s="21" t="n">
+      <x:c r="O19" s="56" t="n">
         <x:v>0.0044</x:v>
       </x:c>
-      <x:c r="P19" s="20" t="n">
+      <x:c r="P19" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="Q19" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R19" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S19" s="20" t="n">
+      <x:c r="Q19" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="T19" s="20" t="n">
+      <x:c r="T19" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="U19" s="19" t="n">
+      <x:c r="U19" s="54" t="n">
         <x:v>192.73</x:v>
       </x:c>
-      <x:c r="V19" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W19" s="19" t="n">
+      <x:c r="V19" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W19" s="54" t="n">
         <x:v>963.65</x:v>
       </x:c>
-      <x:c r="X19" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y19" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z19" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA19" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB19" s="20" t="n">
+      <x:c r="X19" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y19" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA19" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB19" s="55" t="n">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="AC19" s="20" t="n">
+      <x:c r="AC19" s="55" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="AD19" s="20" t="n">
+      <x:c r="AD19" s="55" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="AE19" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF19" s="20" t="n">
+      <x:c r="AE19" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF19" s="55" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="AG19" s="20" t="n">
+      <x:c r="AG19" s="55" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="AH19" s="19" t="n">
+      <x:c r="AH19" s="54" t="n">
         <x:v>43.8</x:v>
       </x:c>
-      <x:c r="AI19" s="21" t="n">
+      <x:c r="AI19" s="56" t="n">
         <x:v>0.0542</x:v>
+      </x:c>
+      <x:c r="AJ19" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK19" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL19" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
@@ -2656,112 +2938,130 @@
       <x:c r="AI20" s="16" t="n">
         <x:v>0.0574</x:v>
       </x:c>
+      <x:c r="AJ20" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK20" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL20" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
-      <x:c r="A21" s="17" t="str">
+      <x:c r="A21" s="52" t="str">
         <x:v>2026-10-18 20:00 - 20:59</x:v>
       </x:c>
-      <x:c r="B21" s="18" t="d">
+      <x:c r="B21" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="str">
+      <x:c r="C21" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D21" s="19" t="n">
+      <x:c r="D21" s="54" t="n">
         <x:v>933.56</x:v>
       </x:c>
-      <x:c r="E21" s="20" t="n">
+      <x:c r="E21" s="55" t="n">
         <x:v>8335</x:v>
       </x:c>
-      <x:c r="F21" s="19" t="n">
+      <x:c r="F21" s="54" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G21" s="20" t="n">
+      <x:c r="G21" s="55" t="n">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="H21" s="21" t="n">
+      <x:c r="H21" s="56" t="n">
         <x:v>0.0275</x:v>
       </x:c>
-      <x:c r="I21" s="19" t="n">
+      <x:c r="I21" s="54" t="n">
         <x:v>4.08</x:v>
       </x:c>
-      <x:c r="J21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L21" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O21" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P21" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T21" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U21" s="19" t="n">
+      <x:c r="J21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T21" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U21" s="54" t="n">
         <x:v>933.56</x:v>
       </x:c>
-      <x:c r="V21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA21" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB21" s="20" t="n">
+      <x:c r="V21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB21" s="55" t="n">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="AC21" s="20" t="n">
+      <x:c r="AC21" s="55" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="AD21" s="20" t="n">
+      <x:c r="AD21" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AE21" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF21" s="20" t="n">
+      <x:c r="AE21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF21" s="55" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AG21" s="20" t="n">
+      <x:c r="AG21" s="55" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="AH21" s="19" t="n">
+      <x:c r="AH21" s="54" t="n">
         <x:v>35.91</x:v>
       </x:c>
-      <x:c r="AI21" s="21" t="n">
+      <x:c r="AI21" s="56" t="n">
         <x:v>0.0745</x:v>
+      </x:c>
+      <x:c r="AJ21" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK21" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL21" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -2870,112 +3170,130 @@
       <x:c r="AI22" s="16" t="n">
         <x:v>0.0682</x:v>
       </x:c>
+      <x:c r="AJ22" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK22" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL22" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
-      <x:c r="A23" s="17" t="str">
+      <x:c r="A23" s="52" t="str">
         <x:v>2026-10-18 12:00 - 12:59</x:v>
       </x:c>
-      <x:c r="B23" s="18" t="d">
+      <x:c r="B23" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="str">
+      <x:c r="C23" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="n">
+      <x:c r="D23" s="54" t="n">
         <x:v>929.06</x:v>
       </x:c>
-      <x:c r="E23" s="20" t="n">
+      <x:c r="E23" s="55" t="n">
         <x:v>4799</x:v>
       </x:c>
-      <x:c r="F23" s="19" t="n">
+      <x:c r="F23" s="54" t="n">
         <x:v>193.59</x:v>
       </x:c>
-      <x:c r="G23" s="20" t="n">
+      <x:c r="G23" s="55" t="n">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="H23" s="21" t="n">
+      <x:c r="H23" s="56" t="n">
         <x:v>0.039</x:v>
       </x:c>
-      <x:c r="I23" s="19" t="n">
+      <x:c r="I23" s="54" t="n">
         <x:v>4.97</x:v>
       </x:c>
-      <x:c r="J23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L23" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O23" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P23" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S23" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T23" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U23" s="19" t="n">
+      <x:c r="J23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L23" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O23" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P23" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S23" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T23" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U23" s="54" t="n">
         <x:v>929.06</x:v>
       </x:c>
-      <x:c r="V23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA23" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB23" s="20" t="n">
+      <x:c r="V23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB23" s="55" t="n">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="AC23" s="20" t="n">
+      <x:c r="AC23" s="55" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="AD23" s="20" t="n">
+      <x:c r="AD23" s="55" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE23" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF23" s="20" t="n">
+      <x:c r="AE23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF23" s="55" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="AG23" s="20" t="n">
+      <x:c r="AG23" s="55" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="AH23" s="19" t="n">
+      <x:c r="AH23" s="54" t="n">
         <x:v>61.94</x:v>
       </x:c>
-      <x:c r="AI23" s="21" t="n">
+      <x:c r="AI23" s="56" t="n">
         <x:v>0.049</x:v>
+      </x:c>
+      <x:c r="AJ23" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK23" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL23" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -3084,112 +3402,130 @@
       <x:c r="AI24" s="16" t="n">
         <x:v>0.060700000000000004</x:v>
       </x:c>
+      <x:c r="AJ24" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK24" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL24" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
-      <x:c r="A25" s="17" t="str">
+      <x:c r="A25" s="52" t="str">
         <x:v>2026-10-18 18:00 - 18:59</x:v>
       </x:c>
-      <x:c r="B25" s="18" t="d">
+      <x:c r="B25" s="53" t="d">
         <x:v>2026-10-18T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C25" s="17" t="str">
+      <x:c r="C25" s="52" t="str">
         <x:v>2026-10</x:v>
       </x:c>
-      <x:c r="D25" s="19" t="n">
+      <x:c r="D25" s="54" t="n">
         <x:v>772.82</x:v>
       </x:c>
-      <x:c r="E25" s="20" t="n">
+      <x:c r="E25" s="55" t="n">
         <x:v>6606</x:v>
       </x:c>
-      <x:c r="F25" s="19" t="n">
+      <x:c r="F25" s="54" t="n">
         <x:v>116.99</x:v>
       </x:c>
-      <x:c r="G25" s="20" t="n">
+      <x:c r="G25" s="55" t="n">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H25" s="21" t="n">
+      <x:c r="H25" s="56" t="n">
         <x:v>0.0297</x:v>
       </x:c>
-      <x:c r="I25" s="19" t="n">
+      <x:c r="I25" s="54" t="n">
         <x:v>3.94</x:v>
       </x:c>
-      <x:c r="J25" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K25" s="19" t="n">
+      <x:c r="J25" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K25" s="54" t="n">
         <x:v>772.82</x:v>
       </x:c>
-      <x:c r="L25" s="21" t="n">
+      <x:c r="L25" s="56" t="n">
         <x:v>0.0051</x:v>
       </x:c>
-      <x:c r="M25" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N25" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O25" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P25" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q25" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R25" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S25" s="20" t="n">
+      <x:c r="M25" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O25" s="56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P25" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q25" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R25" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S25" s="55" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="T25" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U25" s="19" t="n">
+      <x:c r="T25" s="55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U25" s="54" t="n">
         <x:v>772.82</x:v>
       </x:c>
-      <x:c r="V25" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W25" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X25" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y25" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z25" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA25" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB25" s="20" t="n">
+      <x:c r="V25" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB25" s="55" t="n">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="AC25" s="20" t="n">
+      <x:c r="AC25" s="55" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AD25" s="20" t="n">
+      <x:c r="AD25" s="55" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="AE25" s="20" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF25" s="20" t="n">
+      <x:c r="AE25" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF25" s="55" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="AG25" s="20" t="n">
+      <x:c r="AG25" s="55" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="AH25" s="19" t="n">
+      <x:c r="AH25" s="54" t="n">
         <x:v>38.64</x:v>
       </x:c>
-      <x:c r="AI25" s="21" t="n">
+      <x:c r="AI25" s="56" t="n">
         <x:v>0.06269999999999999</x:v>
+      </x:c>
+      <x:c r="AJ25" s="55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK25" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL25" s="56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -3298,108 +3634,126 @@
       <x:c r="AI26" s="16" t="n">
         <x:v>0.0771</x:v>
       </x:c>
+      <x:c r="AJ26" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK26" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL26" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
-      <x:c r="A27" s="32" t="str">
+      <x:c r="A27" s="57" t="str">
         <x:v>接口汇总</x:v>
       </x:c>
-      <x:c r="B27" s="33"/>
-      <x:c r="C27" s="32"/>
-      <x:c r="D27" s="34" t="n">
+      <x:c r="B27" s="58"/>
+      <x:c r="C27" s="57"/>
+      <x:c r="D27" s="59" t="n">
         <x:v>31698.78</x:v>
       </x:c>
-      <x:c r="E27" s="35" t="n">
+      <x:c r="E27" s="60" t="n">
         <x:v>221332</x:v>
       </x:c>
-      <x:c r="F27" s="34" t="n">
+      <x:c r="F27" s="59" t="n">
         <x:v>143.22</x:v>
       </x:c>
-      <x:c r="G27" s="35" t="n">
+      <x:c r="G27" s="60" t="n">
         <x:v>6610</x:v>
       </x:c>
-      <x:c r="H27" s="36" t="n">
+      <x:c r="H27" s="61" t="n">
         <x:v>0.029900000000000003</x:v>
       </x:c>
-      <x:c r="I27" s="34" t="n">
+      <x:c r="I27" s="59" t="n">
         <x:v>4.8</x:v>
       </x:c>
-      <x:c r="J27" s="35" t="n">
+      <x:c r="J27" s="60" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K27" s="34" t="n">
+      <x:c r="K27" s="59" t="n">
         <x:v>1981.17</x:v>
       </x:c>
-      <x:c r="L27" s="36" t="n">
+      <x:c r="L27" s="61" t="n">
         <x:v>0.0024</x:v>
       </x:c>
-      <x:c r="M27" s="35" t="n">
+      <x:c r="M27" s="60" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N27" s="34" t="n">
+      <x:c r="N27" s="59" t="n">
         <x:v>1981.17</x:v>
       </x:c>
-      <x:c r="O27" s="36" t="n">
+      <x:c r="O27" s="61" t="n">
         <x:v>0.0024</x:v>
       </x:c>
-      <x:c r="P27" s="35" t="n">
+      <x:c r="P27" s="60" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="Q27" s="35" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R27" s="35" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S27" s="35" t="n">
+      <x:c r="Q27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S27" s="60" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="T27" s="35" t="n">
+      <x:c r="T27" s="60" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="U27" s="34" t="n">
+      <x:c r="U27" s="59" t="n">
         <x:v>720.43</x:v>
       </x:c>
-      <x:c r="V27" s="35" t="n">
+      <x:c r="V27" s="60" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="W27" s="34" t="n">
+      <x:c r="W27" s="59" t="n">
         <x:v>1981.17</x:v>
       </x:c>
-      <x:c r="X27" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y27" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z27" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA27" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB27" s="35" t="n">
+      <x:c r="X27" s="59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y27" s="59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z27" s="59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA27" s="59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB27" s="60" t="n">
         <x:v>7533</x:v>
       </x:c>
-      <x:c r="AC27" s="35" t="n">
+      <x:c r="AC27" s="60" t="n">
         <x:v>1936</x:v>
       </x:c>
-      <x:c r="AD27" s="35" t="n">
+      <x:c r="AD27" s="60" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="AE27" s="35" t="n">
+      <x:c r="AE27" s="60" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="AF27" s="35" t="n">
+      <x:c r="AF27" s="60" t="n">
         <x:v>1034</x:v>
       </x:c>
-      <x:c r="AG27" s="35" t="n">
+      <x:c r="AG27" s="60" t="n">
         <x:v>878</x:v>
       </x:c>
-      <x:c r="AH27" s="34" t="n">
+      <x:c r="AH27" s="59" t="n">
         <x:v>36.1</x:v>
       </x:c>
-      <x:c r="AI27" s="36" t="n">
+      <x:c r="AI27" s="61" t="n">
         <x:v>0.0855</x:v>
+      </x:c>
+      <x:c r="AJ27" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK27" s="59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL27" s="61" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3410,7 +3764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d0a491ad55f4b7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R203cb5a2e45d4ff1"/>
   </x:tableParts>
 </x:worksheet>
 </file>